--- a/data/高质量作品历史库.xlsx
+++ b/data/高质量作品历史库.xlsx
@@ -22,7 +22,7 @@
     <t>质量指数 ≥ 80 作品历史库（URL 去重）</t>
   </si>
   <si>
-    <t>生成时间：2026-08-12T05:50:26+00:00。每天合并质量指数大于等于 80 的公开榜单作品；同一作品仅保留一条记录，并更新最近数据与达标日期。</t>
+    <t>生成时间：2026-08-13T05:52:12+00:00。每天合并质量指数大于等于 80 的公开榜单作品；同一作品仅保留一条记录，并更新最近数据与达标日期。</t>
   </si>
   <si>
     <t>作品名</t>

--- a/data/高质量作品历史库.xlsx
+++ b/data/高质量作品历史库.xlsx
@@ -22,7 +22,7 @@
     <t>质量指数 ≥ 80 作品历史库（URL 去重）</t>
   </si>
   <si>
-    <t>生成时间：2026-08-23T01:51:57+00:00。每天合并质量指数大于等于 80 的公开榜单作品；同一作品仅保留一条记录，并更新最近数据与达标日期。</t>
+    <t>生成时间：2026-08-24T01:47:22+00:00。每天合并质量指数大于等于 80 的公开榜单作品；同一作品仅保留一条记录，并更新最近数据与达标日期。</t>
   </si>
   <si>
     <t>作品名</t>
